--- a/public/sap-reporting/expansion-150-downloads/EXT-PP20-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PP20-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rb09fb9ac5b564549"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R337f2ea2d699409c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R26749c642f684f8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R764bf7daaf6f431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rebeb9049c71b4391"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R22d6c0000b8d4385"/>
   </x:sheets>
 </x:workbook>
 </file>
